--- a/2026-09-28/端游三源周报_大报告_2026-09-28.xlsx
+++ b/2026-09-28/端游三源周报_大报告_2026-09-28.xlsx
@@ -21258,7 +21258,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>**对比基准已按用户要求改为「本期两周 vs 上期两周」**。判定依据：405 款共有游戏的「本期 14 天合计 ÷ 上期 2 天合计」比值中位数为 1.014 ≈ 1，说明上期那 2 个日期列是周汇总而非单日，两者时间跨度等效、可直接比。</t>
+          <t>对比基准已按用户要求改为「本期两周 vs 上期两周」。判定依据：405 款共有游戏的「本期 14 天合计 ÷ 上期 2 天合计」比值中位数为 1.014 ≈ 1，说明上期那 2 个日期列是周汇总而非单日，两者时间跨度等效、可直接比。</t>
         </is>
       </c>
     </row>
